--- a/secure_report/reports/テスト項目書_20260702.xlsx
+++ b/secure_report/reports/テスト項目書_20260702.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\proj\nichiben\secure_report\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1025966D-EFBE-4140-846F-60A62039E1B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67EBF1AD-F086-4DB9-B768-109B50C296AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="165" yWindow="0" windowWidth="20370" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テスト項目書 Ph.1-Ph.23" sheetId="1" r:id="rId1"/>
@@ -506,9 +506,6 @@
     <t>アラートが発生しない。HTML Purifier により &lt;img src=x onerror=...&gt; タグが除去され、スクリプトが無効化される。改行のみ &lt;br&gt; に変換されて表示される</t>
   </si>
   <si>
-    <t>CSRF-01</t>
-  </si>
-  <si>
     <t>CSRF</t>
   </si>
   <si>
@@ -697,9 +694,6 @@
     <t>マルチタブ操作・ブラウザ「戻る」後の再送信でもCSRFエラーが発生しない</t>
   </si>
   <si>
-    <t>SQLI-01</t>
-  </si>
-  <si>
     <t>SQLi</t>
   </si>
   <si>
@@ -707,15 +701,6 @@
   </si>
   <si>
     <t>Ph.15</t>
-  </si>
-  <si>
-    <t>1. CMS 商品一覧を開く
-2. 検索フォームの開始日または終了日にテストデータを入力して「検索」をクリックする
-3. SQLエラーメッセージが画面またはHTMLソースに表示されないことを確認する
-4. HTTP 200 で正常な結果（空の一覧可）が返ることを確認する</t>
-  </si>
-  <si>
-    <t>' OR '1'='1</t>
   </si>
   <si>
     <t>SQLエラーが表示されない。通常の検索結果または空の一覧が返る</t>
@@ -796,10 +781,6 @@
   </si>
   <si>
     <t>F-15b</t>
-  </si>
-  <si>
-    <t>1. https://api.nichibenren-stg2.alfcloud.com/debug.php に直接アクセスする
-2. 404 またはアクセス拒否が返ることを確認する</t>
   </si>
   <si>
     <t>— アクセステストのみ</t>
@@ -857,9 +838,6 @@
     <t>CSVファイルが正常にダウンロードされる。デバッグ出力（var_dump 等）が含まれない</t>
   </si>
   <si>
-    <t>HDR-01</t>
-  </si>
-  <si>
     <t>ヘッダー</t>
   </si>
   <si>
@@ -875,19 +853,10 @@
     <t>CMS-M-01〜03</t>
   </si>
   <si>
-    <t>1. ターミナルで実行: curl -I https://cms.nichibenren-stg2.alfcloud.com/
-2. （またはブラウザDevTools › Network › 任意リクエストを選択 › Response Headers を確認）
-3. Cross-Origin-Opener-Policy ヘッダーが存在することを確認する
-4. Cross-Origin-Resource-Policy ヘッダーが存在することを確認する</t>
-  </si>
-  <si>
     <t>curl -I https://cms.nichibenren-stg2.alfcloud.com/</t>
   </si>
   <si>
     <t>Cross-Origin-Opener-Policy・Cross-Origin-Resource-Policy の2ヘッダーがすべてレスポンスに存在する</t>
-  </si>
-  <si>
-    <t>HDR-02</t>
   </si>
   <si>
     <t>受講者サイト トップ（HTTPレスポンスヘッダー確認）</t>
@@ -922,9 +891,6 @@
     <t>Content-Security-Policy ヘッダーが存在する</t>
   </si>
   <si>
-    <t>HDR-04</t>
-  </si>
-  <si>
     <t>STU-L-01</t>
   </si>
   <si>
@@ -952,9 +918,6 @@
 2. Referrer-Policy ヘッダーが存在することを確認する
 3. 値が strict-origin-when-cross-origin であることを確認する
 4. 同様に curl -I https://nichibenren-stg2.alfcloud.com/ を実行して同ヘッダーと値を確認する</t>
-  </si>
-  <si>
-    <t>curl -I https://cms.nichibenren-stg2.alfcloud.com/（受講者サイトも同様）</t>
   </si>
   <si>
     <t>Referrer-Policy: strict-origin-when-cross-origin がレスポンスに存在する</t>
@@ -991,12 +954,6 @@
     <t>SameSite=Strict・HttpOnly=true・Secure=true がすべて設定されている</t>
   </si>
   <si>
-    <t>SSOのみのため検証不可</t>
-  </si>
-  <si>
-    <t>SESS-02</t>
-  </si>
-  <si>
     <t>CMSログイン後 各画面</t>
   </si>
   <si>
@@ -1013,9 +970,6 @@
 5. 同 Cookie の Secure 列に ✓ が表示されていることを確認する</t>
   </si>
   <si>
-    <t>REDIR-01</t>
-  </si>
-  <si>
     <t>リダイレクト</t>
   </si>
   <si>
@@ -1039,23 +993,12 @@
     <t>外部ドメインへのリダイレクトが発生しない。エラーページまたはデフォルトURLへ遷移する</t>
   </si>
   <si>
-    <t>REDIR-02</t>
-  </si>
-  <si>
     <t>SSOログイン（新版） /login_sso_new.php</t>
   </si>
   <si>
     <t>/login_sso_new.php</t>
   </si>
   <si>
-    <t>1. ブラウザまたは curl で https://nichibenren-stg2.alfcloud.com/login_sso_new.php?burl=https://evil.example.com にアクセスする
-2. 外部ドメイン（evil.example.com）へのリダイレクトが発生しないことを確認する
-3. エラーページまたはシステム内のデフォルトURLへ遷移することを確認する</t>
-  </si>
-  <si>
-    <t>INPUT-01</t>
-  </si>
-  <si>
     <t>入力検証</t>
   </si>
   <si>
@@ -1071,10 +1014,6 @@
     <t>CMS-L-02</t>
   </si>
   <si>
-    <t>1. CMSの検索フォームのPOSTパラメータをURLクエリ文字列（GET）に付けてアクセスする: /product/index?keyword=testval
-2. GET パラメータが処理されていないことを確認する（検索結果に "testval" が反映されない）</t>
-  </si>
-  <si>
     <t>URL: /product/index?keyword=testval</t>
   </si>
   <si>
@@ -1093,17 +1032,10 @@
     <t>STU-L-02</t>
   </si>
   <si>
-    <t>1. 受講者サイトの検索フォームのPOSTパラメータをGETで付けてアクセスする: /search/index.php?keyword=testval
-2. GET パラメータが処理されていないことを確認する</t>
-  </si>
-  <si>
     <t>URL: /search/index.php?keyword=testval</t>
   </si>
   <si>
     <t>GET パラメータが無視される。$_GET 値が検索結果に影響しない</t>
-  </si>
-  <si>
-    <t>INPUT-03</t>
   </si>
   <si>
     <t>CMS トップ / 受講者サイト トップ / API トップ</t>
@@ -1125,9 +1057,6 @@
   </si>
   <si>
     <t>HTTP 405 Method Not Allowed が返る</t>
-  </si>
-  <si>
-    <t>LINK-01</t>
   </si>
   <si>
     <t>リンク安全性</t>
@@ -1323,6 +1252,109 @@
   </si>
   <si>
     <t>Content-Security-Policy ヘッダーが存在する</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>受講者側はSSOからのログインのみのためStrict設定不可</t>
+    <rPh sb="0" eb="3">
+      <t>ジュコウシャ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ガワ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>フカ</t>
+    </rPh>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>CSRF-01</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> OR '1'='1</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>1. CMS 商品一覧を開く
+2. 検索フォームの開始日または終了日にテストデータを入力して「検索」をクリックする
+3. SQLエラーメッセージが画面またはHTMLソースに表示されないことを確認する
+4. HTTP 200 で正常な結果（空の一覧可）が返ることを確認する</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>SQLI-01</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>1. https://api.nichibenren-stg2.alfcloud.com/debug.php に直接アクセスする
+2. 404 またはアクセス拒否が返ることを確認する</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>1. ターミナルで実行: curl -I https://cms.nichibenren-stg2.alfcloud.com/
+2. （またはブラウザDevTools › Network › 任意リクエストを選択 › Response Headers を確認）
+3. Cross-Origin-Opener-Policy ヘッダーが存在することを確認する
+4. Cross-Origin-Resource-Policy ヘッダーが存在することを確認する</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>HDR-01</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>HDR-02</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>HDR-04</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>curl -I https://cms.nichibenren-stg2.alfcloud.com/（受講者サイトも同様）</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>SESS-02</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>REDIR-01</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>REDIR-02</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>1. ブラウザまたは curl で https://nichibenren-stg2.alfcloud.com/login_sso_new.php?burl=https://evil.example.com にアクセスする
+2. 外部ドメイン（evil.example.com）へのリダイレクトが発生しないことを確認する
+3. エラーページまたはシステム内のデフォルトURLへ遷移することを確認する</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>1. CMSの検索フォームのPOSTパラメータをURLクエリ文字列（GET）に付けてアクセスする: /product/index?keyword=testval
+2. GET パラメータが処理されていないことを確認する（検索結果に "testval" が反映されない）</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>INPUT-01</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>1. 受講者サイトの検索フォームのPOSTパラメータをGETで付けてアクセスする: /search/index.php?keyword=testval
+2. GET パラメータが処理されていないことを確認する</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>LINK-01</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>INPUT-03</t>
     <phoneticPr fontId="26"/>
   </si>
 </sst>
@@ -1624,7 +1656,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1751,6 +1783,12 @@
         <fgColor rgb="FFFFF9DB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -1850,7 +1888,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2005,6 +2043,21 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2948,34 +3001,34 @@
     </row>
     <row r="18" spans="1:12" ht="98.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="B18" s="13" t="s">
         <v>142</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>143</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D18" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>144</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>145</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>50</v>
       </c>
       <c r="G18" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="H18" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="I18" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="I18" s="7" t="s">
+      <c r="J18" s="7" t="s">
         <v>148</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>149</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>22</v>
@@ -2984,34 +3037,34 @@
     </row>
     <row r="19" spans="1:12" ht="57" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D19" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="F19" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="G19" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="H19" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="H19" s="5" t="s">
+      <c r="I19" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="I19" s="5" t="s">
+      <c r="J19" s="5" t="s">
         <v>155</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>156</v>
       </c>
       <c r="K19" s="6" t="s">
         <v>22</v>
@@ -3020,34 +3073,34 @@
     </row>
     <row r="20" spans="1:12" ht="71.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="E20" s="7" t="s">
         <v>158</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>159</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>50</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H20" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="I20" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="I20" s="7" t="s">
+      <c r="J20" s="7" t="s">
         <v>161</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>162</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>22</v>
@@ -3056,34 +3109,34 @@
     </row>
     <row r="21" spans="1:12" ht="171" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>32</v>
       </c>
       <c r="D21" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E21" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="F21" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="G21" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="H21" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="I21" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="J21" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>22</v>
@@ -3092,34 +3145,34 @@
     </row>
     <row r="22" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D22" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E22" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="F22" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="G22" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="G22" s="7" t="s">
+      <c r="H22" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="H22" s="7" t="s">
+      <c r="I22" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="J22" s="7" t="s">
         <v>175</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>176</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>22</v>
@@ -3128,34 +3181,34 @@
     </row>
     <row r="23" spans="1:12" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>32</v>
       </c>
       <c r="D23" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="F23" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="F23" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="G23" s="5" t="s">
+      <c r="H23" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="I23" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="J23" s="5" t="s">
         <v>181</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>182</v>
       </c>
       <c r="K23" s="6" t="s">
         <v>22</v>
@@ -3164,34 +3217,34 @@
     </row>
     <row r="24" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="B24" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="C24" s="13" t="s">
+      <c r="D24" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="E24" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="F24" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="G24" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="G24" s="7" t="s">
+      <c r="H24" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="H24" s="7" t="s">
+      <c r="I24" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="I24" s="7" t="s">
+      <c r="J24" s="7" t="s">
         <v>190</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>191</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>22</v>
@@ -3200,34 +3253,34 @@
     </row>
     <row r="25" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D25" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>193</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>194</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>50</v>
       </c>
       <c r="G25" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="H25" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="H25" s="5" t="s">
+      <c r="I25" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="I25" s="5" t="s">
+      <c r="J25" s="5" t="s">
         <v>197</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>198</v>
       </c>
       <c r="K25" s="6" t="s">
         <v>22</v>
@@ -3236,34 +3289,34 @@
     </row>
     <row r="26" spans="1:12" ht="57" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="14" t="s">
-        <v>199</v>
+        <v>364</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G26" s="7" t="s">
         <v>18</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>204</v>
+        <v>363</v>
+      </c>
+      <c r="I26" s="58" t="s">
+        <v>362</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="K26" s="6" t="s">
         <v>22</v>
@@ -3272,34 +3325,34 @@
     </row>
     <row r="27" spans="1:12" ht="71.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="16" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>32</v>
       </c>
       <c r="D27" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="H27" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="I27" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="J27" s="5" t="s">
         <v>209</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="J27" s="5" t="s">
-        <v>213</v>
       </c>
       <c r="K27" s="6" t="s">
         <v>22</v>
@@ -3308,10 +3361,10 @@
     </row>
     <row r="28" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="16" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>112</v>
@@ -3323,13 +3376,13 @@
         <v>114</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="I28" s="10" t="s">
         <v>112</v>
@@ -3341,77 +3394,77 @@
         <v>63</v>
       </c>
       <c r="L28" s="10" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="16" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>32</v>
       </c>
       <c r="D29" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="I29" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="J29" s="5" t="s">
         <v>220</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="J29" s="5" t="s">
-        <v>224</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>63</v>
       </c>
       <c r="L29" s="5" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="83.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="16" t="s">
+        <v>222</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="I30" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="B30" s="17" t="s">
-        <v>207</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="D30" s="7" t="s">
+      <c r="J30" s="7" t="s">
         <v>227</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="J30" s="7" t="s">
-        <v>232</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>22</v>
@@ -3420,34 +3473,34 @@
     </row>
     <row r="31" spans="1:12" ht="128.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="16" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>22</v>
@@ -3456,34 +3509,34 @@
     </row>
     <row r="32" spans="1:12" ht="57" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="I32" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="B32" s="17" t="s">
-        <v>207</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="D32" s="7" t="s">
+      <c r="J32" s="7" t="s">
         <v>241</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>246</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>22</v>
@@ -3492,34 +3545,34 @@
     </row>
     <row r="33" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="18" t="s">
-        <v>247</v>
+        <v>367</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>253</v>
+        <v>366</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>22</v>
@@ -3528,34 +3581,34 @@
     </row>
     <row r="34" spans="1:12" ht="71.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="18" t="s">
-        <v>256</v>
+        <v>368</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>32</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="F34" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="G34" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="G34" s="7" t="s">
-        <v>259</v>
-      </c>
       <c r="H34" s="7" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>22</v>
@@ -3564,34 +3617,34 @@
     </row>
     <row r="35" spans="1:12" ht="57" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="18" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>379</v>
+        <v>359</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>22</v>
@@ -3600,34 +3653,34 @@
     </row>
     <row r="36" spans="1:12" ht="57" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="18" t="s">
-        <v>266</v>
+        <v>369</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>32</v>
       </c>
       <c r="D36" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="J36" s="7" t="s">
         <v>257</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="H36" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="I36" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="J36" s="7" t="s">
-        <v>265</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>22</v>
@@ -3636,34 +3689,34 @@
     </row>
     <row r="37" spans="1:12" ht="71.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="18" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>275</v>
+        <v>370</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>22</v>
@@ -3671,73 +3724,73 @@
       <c r="L37" s="5"/>
     </row>
     <row r="38" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="20" t="s">
-        <v>277</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="C38" s="8" t="s">
+      <c r="A38" s="54" t="s">
+        <v>267</v>
+      </c>
+      <c r="B38" s="55" t="s">
+        <v>268</v>
+      </c>
+      <c r="C38" s="55" t="s">
         <v>32</v>
       </c>
-      <c r="D38" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="H38" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="I38" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="J38" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="K38" s="6" t="s">
+      <c r="D38" s="56" t="s">
+        <v>269</v>
+      </c>
+      <c r="E38" s="56" t="s">
+        <v>270</v>
+      </c>
+      <c r="F38" s="56" t="s">
+        <v>271</v>
+      </c>
+      <c r="G38" s="56" t="s">
+        <v>272</v>
+      </c>
+      <c r="H38" s="56" t="s">
+        <v>273</v>
+      </c>
+      <c r="I38" s="56" t="s">
+        <v>274</v>
+      </c>
+      <c r="J38" s="56" t="s">
+        <v>275</v>
+      </c>
+      <c r="K38" s="57" t="s">
         <v>63</v>
       </c>
-      <c r="L38" s="7" t="s">
-        <v>286</v>
+      <c r="L38" s="56" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="20" t="s">
-        <v>287</v>
+        <v>371</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>22</v>
@@ -3746,34 +3799,34 @@
     </row>
     <row r="40" spans="1:12" ht="57" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="21" t="s">
-        <v>292</v>
+        <v>372</v>
       </c>
       <c r="B40" s="22" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>32</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>298</v>
+        <v>285</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>22</v>
@@ -3782,34 +3835,34 @@
     </row>
     <row r="41" spans="1:12" ht="57" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="21" t="s">
-        <v>300</v>
+        <v>373</v>
       </c>
       <c r="B41" s="22" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>32</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>303</v>
+        <v>374</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>298</v>
+        <v>285</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>22</v>
@@ -3818,34 +3871,34 @@
     </row>
     <row r="42" spans="1:12" ht="57" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="23" t="s">
-        <v>304</v>
+        <v>376</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>310</v>
+        <v>375</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>311</v>
+        <v>294</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>22</v>
@@ -3854,34 +3907,34 @@
     </row>
     <row r="43" spans="1:12" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="23" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>32</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>315</v>
+        <v>298</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>317</v>
+        <v>377</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>318</v>
+        <v>300</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>22</v>
@@ -3890,34 +3943,34 @@
     </row>
     <row r="44" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="23" t="s">
-        <v>320</v>
+        <v>379</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>321</v>
+        <v>302</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>322</v>
+        <v>303</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>324</v>
+        <v>305</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>325</v>
+        <v>306</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>326</v>
+        <v>307</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>22</v>
@@ -3926,34 +3979,34 @@
     </row>
     <row r="45" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="41" t="s">
-        <v>327</v>
+        <v>378</v>
       </c>
       <c r="B45" s="42" t="s">
-        <v>328</v>
+        <v>308</v>
       </c>
       <c r="C45" s="43" t="s">
         <v>32</v>
       </c>
       <c r="D45" s="44" t="s">
-        <v>329</v>
+        <v>309</v>
       </c>
       <c r="E45" s="44" t="s">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="F45" s="44" t="s">
-        <v>331</v>
+        <v>311</v>
       </c>
       <c r="G45" s="44" t="s">
-        <v>332</v>
+        <v>312</v>
       </c>
       <c r="H45" s="44" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="I45" s="44" t="s">
-        <v>334</v>
+        <v>314</v>
       </c>
       <c r="J45" s="44" t="s">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="K45" s="6" t="s">
         <v>22</v>
@@ -3962,7 +4015,7 @@
     </row>
     <row r="46" spans="1:12" ht="98.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="45" t="s">
-        <v>336</v>
+        <v>316</v>
       </c>
       <c r="B46" s="46" t="s">
         <v>13</v>
@@ -3971,25 +4024,25 @@
         <v>32</v>
       </c>
       <c r="D46" s="48" t="s">
-        <v>337</v>
+        <v>317</v>
       </c>
       <c r="E46" s="48" t="s">
-        <v>338</v>
+        <v>318</v>
       </c>
       <c r="F46" s="49" t="s">
-        <v>339</v>
+        <v>319</v>
       </c>
       <c r="G46" s="49" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="H46" s="48" t="s">
-        <v>341</v>
+        <v>321</v>
       </c>
       <c r="I46" s="48" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="J46" s="49" t="s">
-        <v>343</v>
+        <v>323</v>
       </c>
       <c r="K46" s="40" t="s">
         <v>22</v>
@@ -3998,7 +4051,7 @@
     </row>
     <row r="47" spans="1:12" ht="114" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="45" t="s">
-        <v>344</v>
+        <v>324</v>
       </c>
       <c r="B47" s="46" t="s">
         <v>13</v>
@@ -4007,25 +4060,25 @@
         <v>32</v>
       </c>
       <c r="D47" s="48" t="s">
-        <v>345</v>
+        <v>325</v>
       </c>
       <c r="E47" s="48" t="s">
-        <v>346</v>
+        <v>326</v>
       </c>
       <c r="F47" s="49" t="s">
-        <v>339</v>
+        <v>319</v>
       </c>
       <c r="G47" s="49" t="s">
-        <v>347</v>
+        <v>327</v>
       </c>
       <c r="H47" s="48" t="s">
-        <v>348</v>
+        <v>328</v>
       </c>
       <c r="I47" s="48" t="s">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="J47" s="49" t="s">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="K47" s="40" t="s">
         <v>22</v>
@@ -4034,7 +4087,7 @@
     </row>
     <row r="48" spans="1:12" ht="98.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="45" t="s">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="B48" s="46" t="s">
         <v>13</v>
@@ -4043,36 +4096,36 @@
         <v>32</v>
       </c>
       <c r="D48" s="48" t="s">
-        <v>351</v>
+        <v>331</v>
       </c>
       <c r="E48" s="48" t="s">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="F48" s="49" t="s">
-        <v>339</v>
+        <v>319</v>
       </c>
       <c r="G48" s="49" t="s">
-        <v>353</v>
+        <v>333</v>
       </c>
       <c r="H48" s="48" t="s">
-        <v>354</v>
+        <v>334</v>
       </c>
       <c r="I48" s="48" t="s">
-        <v>355</v>
+        <v>335</v>
       </c>
       <c r="J48" s="48" t="s">
-        <v>356</v>
+        <v>336</v>
       </c>
       <c r="K48" s="40" t="s">
         <v>63</v>
       </c>
       <c r="L48" s="53" t="s">
-        <v>357</v>
+        <v>337</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="105" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="45" t="s">
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="B49" s="46" t="s">
         <v>13</v>
@@ -4087,30 +4140,30 @@
         <v>136</v>
       </c>
       <c r="F49" s="49" t="s">
-        <v>359</v>
+        <v>339</v>
       </c>
       <c r="G49" s="49" t="s">
         <v>138</v>
       </c>
       <c r="H49" s="49" t="s">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="I49" s="49" t="s">
-        <v>361</v>
+        <v>341</v>
       </c>
       <c r="J49" s="49" t="s">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="K49" s="40" t="s">
         <v>22</v>
       </c>
       <c r="L49" s="39" t="s">
-        <v>363</v>
+        <v>343</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="142.5" x14ac:dyDescent="0.15">
       <c r="A50" s="45" t="s">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="B50" s="46" t="s">
         <v>13</v>
@@ -4119,31 +4172,31 @@
         <v>32</v>
       </c>
       <c r="D50" s="49" t="s">
-        <v>365</v>
+        <v>345</v>
       </c>
       <c r="E50" s="49" t="s">
-        <v>366</v>
+        <v>346</v>
       </c>
       <c r="F50" s="49" t="s">
-        <v>359</v>
+        <v>339</v>
       </c>
       <c r="G50" s="49" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="H50" s="49" t="s">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="I50" s="48" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="J50" s="49" t="s">
-        <v>369</v>
+        <v>349</v>
       </c>
       <c r="K50" s="40" t="s">
         <v>22</v>
       </c>
       <c r="L50" s="53" t="s">
-        <v>376</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -4169,7 +4222,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="25" t="s">
-        <v>370</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4177,7 +4230,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>371</v>
+        <v>351</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -4185,7 +4238,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>372</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -4193,15 +4246,15 @@
         <v>14</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>373</v>
+        <v>353</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="27" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>374</v>
+        <v>354</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -4209,7 +4262,7 @@
         <v>112</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
